--- a/data/trans_orig/Q4501_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q4501_R-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 15 o mayor el pasado verano al aire libre en 2007</t>
+          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 15 o mayor el pasado verano al aire libre en 2007 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>71092</t>
+          <t>69594</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>104929</t>
+          <t>105149</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>79321</t>
+          <t>79958</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>113200</t>
+          <t>112228</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>156969</t>
+          <t>157315</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>207054</t>
+          <t>205958</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71335</t>
+          <t>73549</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>106945</t>
+          <t>106775</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67005</t>
+          <t>68177</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>99194</t>
+          <t>98363</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>150282</t>
+          <t>149939</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>195469</t>
+          <t>196126</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,17%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>116297</t>
+          <t>115655</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>156673</t>
+          <t>154856</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>70869</t>
+          <t>69091</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>101353</t>
+          <t>101599</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>195729</t>
+          <t>196237</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>247014</t>
+          <t>247780</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,8%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43826</t>
+          <t>44173</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73210</t>
+          <t>73386</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13069</t>
+          <t>12820</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31644</t>
+          <t>30521</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>61805</t>
+          <t>62369</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>96557</t>
+          <t>96345</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>88475</t>
+          <t>88539</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>126202</t>
+          <t>125417</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13710</t>
+          <t>13263</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31376</t>
+          <t>31732</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>107909</t>
+          <t>108572</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>150412</t>
+          <t>152396</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,56%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48160</t>
+          <t>46244</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76650</t>
+          <t>76354</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>117338</t>
+          <t>117640</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>155470</t>
+          <t>154176</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>170260</t>
+          <t>172808</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>221197</t>
+          <t>219853</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,84%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43734</t>
+          <t>43050</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71443</t>
+          <t>70424</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63504</t>
+          <t>63763</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95346</t>
+          <t>95544</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>112872</t>
+          <t>113653</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>154027</t>
+          <t>155274</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,08%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>83445</t>
+          <t>85551</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>118111</t>
+          <t>120752</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>71427</t>
+          <t>70867</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>104220</t>
+          <t>104406</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>166483</t>
+          <t>165991</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>214857</t>
+          <t>212724</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>28,87%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38781</t>
+          <t>37077</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67687</t>
+          <t>66589</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14691</t>
+          <t>14670</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34790</t>
+          <t>34891</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56522</t>
+          <t>58797</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90394</t>
+          <t>92347</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,53%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>80195</t>
+          <t>79841</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>115446</t>
+          <t>115052</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35839</t>
+          <t>36222</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62647</t>
+          <t>62428</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,47 +1916,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>16,84%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>144979</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>124490</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>169080</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>19,68%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>16,9%</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>144979</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>125086</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>169592</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>19,68%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>16,98%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,95%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54372</t>
+          <t>54883</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86619</t>
+          <t>86513</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37999</t>
+          <t>38870</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62486</t>
+          <t>61879</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>102172</t>
+          <t>101429</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>140122</t>
+          <t>140525</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,79%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>59282</t>
+          <t>58050</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>93039</t>
+          <t>92268</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30968</t>
+          <t>31362</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53948</t>
+          <t>54104</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>95478</t>
+          <t>93947</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>137101</t>
+          <t>135773</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,12%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>96204</t>
+          <t>96786</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>135343</t>
+          <t>134818</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28955</t>
+          <t>29516</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>131475</t>
+          <t>131700</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>175387</t>
+          <t>176361</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,83%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>74634</t>
+          <t>76911</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>109839</t>
+          <t>110859</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4962</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19058</t>
+          <t>19378</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>85181</t>
+          <t>84876</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>121886</t>
+          <t>125404</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,66%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>172143</t>
+          <t>172380</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>215901</t>
+          <t>216826</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17279</t>
+          <t>17284</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36809</t>
+          <t>36766</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>196493</t>
+          <t>195827</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>243972</t>
+          <t>244900</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,48%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>117634</t>
+          <t>118623</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>163364</t>
+          <t>163321</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>166185</t>
+          <t>163807</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>212530</t>
+          <t>214278</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>291444</t>
+          <t>296875</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>358937</t>
+          <t>364382</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,68%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>117811</t>
+          <t>117832</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>162602</t>
+          <t>163337</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>139678</t>
+          <t>139473</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>187826</t>
+          <t>184314</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>265865</t>
+          <t>268197</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>330858</t>
+          <t>333235</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,08%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>234251</t>
+          <t>232940</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>291402</t>
+          <t>290708</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>126670</t>
+          <t>127547</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>169555</t>
+          <t>168540</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>374085</t>
+          <t>373255</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>445382</t>
+          <t>445227</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,82%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>160341</t>
+          <t>163868</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>212648</t>
+          <t>219283</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>55959</t>
+          <t>55917</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>87859</t>
+          <t>89776</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>233475</t>
+          <t>231204</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>293628</t>
+          <t>290722</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,9%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>470817</t>
+          <t>473641</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>541390</t>
+          <t>541891</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>124290</t>
+          <t>122881</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>167965</t>
+          <t>163445</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>605619</t>
+          <t>609959</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>688863</t>
+          <t>693377</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,54%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>35630</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>62156</t>
+          <t>60587</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>137923</t>
+          <t>137639</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>183343</t>
+          <t>182502</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>180167</t>
+          <t>182096</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>231133</t>
+          <t>234057</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,46%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>22989</t>
+          <t>22812</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>44747</t>
+          <t>44730</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>91949</t>
+          <t>90376</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>129874</t>
+          <t>129028</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>123190</t>
+          <t>120389</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>167447</t>
+          <t>166150</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,07%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>51428</t>
+          <t>52402</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>80654</t>
+          <t>81678</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>91465</t>
+          <t>90692</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>130336</t>
+          <t>128884</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>148413</t>
+          <t>151870</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>199377</t>
+          <t>198509</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,59%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>31003</t>
+          <t>30481</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>55714</t>
+          <t>56209</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>37071</t>
+          <t>36775</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>66458</t>
+          <t>66922</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>72729</t>
+          <t>73623</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>111273</t>
+          <t>111833</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>144965</t>
+          <t>142268</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>181367</t>
+          <t>181751</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>120723</t>
+          <t>121636</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>162456</t>
+          <t>162327</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>276625</t>
+          <t>276585</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>332340</t>
+          <t>333528</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,28%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>25006</t>
+          <t>26401</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>48284</t>
+          <t>48265</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>276020</t>
+          <t>275886</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>337016</t>
+          <t>336393</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>310728</t>
+          <t>310974</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>376503</t>
+          <t>377945</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>26290</t>
+          <t>26495</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>47041</t>
+          <t>48031</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>187755</t>
+          <t>188013</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>238298</t>
+          <t>239598</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>221203</t>
+          <t>218173</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>278944</t>
+          <t>277988</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>73199</t>
+          <t>72139</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>102484</t>
+          <t>101875</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>229393</t>
+          <t>230426</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>287169</t>
+          <t>287306</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>313377</t>
+          <t>314039</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>378970</t>
+          <t>377751</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,45%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>35468</t>
+          <t>35479</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>59995</t>
+          <t>60799</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>76732</t>
+          <t>77624</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>112401</t>
+          <t>114163</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>120034</t>
+          <t>117802</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>163321</t>
+          <t>164206</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>77480</t>
+          <t>79168</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>107445</t>
+          <t>108662</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>345376</t>
+          <t>345109</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>410402</t>
+          <t>406091</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>434926</t>
+          <t>435269</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>508310</t>
+          <t>505714</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,73%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>404924</t>
+          <t>405327</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>483664</t>
+          <t>480522</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>880844</t>
+          <t>884718</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>984624</t>
+          <t>990172</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1308450</t>
+          <t>1307653</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1440826</t>
+          <t>1444002</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,74%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>386894</t>
+          <t>389471</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>465278</t>
+          <t>463913</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>634704</t>
+          <t>642915</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>733687</t>
+          <t>734185</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1053121</t>
+          <t>1052151</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1177304</t>
+          <t>1173393</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,67%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>715322</t>
+          <t>714978</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>812776</t>
+          <t>813754</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>678144</t>
+          <t>681131</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>774185</t>
+          <t>775428</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1422535</t>
+          <t>1431122</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1563003</t>
+          <t>1562124</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>433406</t>
+          <t>435209</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>519187</t>
+          <t>518656</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>241431</t>
+          <t>238517</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>303317</t>
+          <t>303326</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>699728</t>
+          <t>702120</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>802896</t>
+          <t>802901</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1106312</t>
+          <t>1103348</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1214420</t>
+          <t>1220120</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>709866</t>
+          <t>707647</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>808709</t>
+          <t>803962</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1837419</t>
+          <t>1840520</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1991958</t>
+          <t>1987923</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,93%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 15 o mayor el pasado verano al aire libre en 2012</t>
+          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 15 o mayor el pasado verano al aire libre en 2012 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44028</t>
+          <t>44580</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>73572</t>
+          <t>74292</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>82604</t>
+          <t>82666</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>117444</t>
+          <t>118098</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>135597</t>
+          <t>133413</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>179100</t>
+          <t>180716</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47858</t>
+          <t>47600</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77109</t>
+          <t>77459</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68226</t>
+          <t>65867</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>101653</t>
+          <t>99083</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>122460</t>
+          <t>120665</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>166921</t>
+          <t>167670</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>111840</t>
+          <t>111968</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>152237</t>
+          <t>153711</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>51428</t>
+          <t>52283</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>81858</t>
+          <t>82477</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>173493</t>
+          <t>172129</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>224853</t>
+          <t>223433</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,8%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44413</t>
+          <t>44392</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74878</t>
+          <t>73334</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11557</t>
+          <t>11535</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29612</t>
+          <t>29086</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>60847</t>
+          <t>60744</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>94614</t>
+          <t>96572</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>110494</t>
+          <t>109349</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>154044</t>
+          <t>148622</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33974</t>
+          <t>33822</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59934</t>
+          <t>59952</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>152652</t>
+          <t>151853</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>202496</t>
+          <t>200627</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,76%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44892</t>
+          <t>45578</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75686</t>
+          <t>75836</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>71984</t>
+          <t>72924</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>108524</t>
+          <t>109455</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>126566</t>
+          <t>127509</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>172897</t>
+          <t>174373</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,07%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47761</t>
+          <t>48484</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80533</t>
+          <t>80485</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62453</t>
+          <t>63471</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95756</t>
+          <t>95867</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>119698</t>
+          <t>120207</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>164732</t>
+          <t>164184</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,72%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>112403</t>
+          <t>112090</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>151872</t>
+          <t>154996</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>67912</t>
+          <t>67361</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>100944</t>
+          <t>101100</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>186406</t>
+          <t>188388</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>240772</t>
+          <t>240066</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,76%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24584</t>
+          <t>25395</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49821</t>
+          <t>51112</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>13358</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32914</t>
+          <t>33833</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41941</t>
+          <t>42062</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74715</t>
+          <t>72616</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>108948</t>
+          <t>110131</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>150167</t>
+          <t>152136</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50555</t>
+          <t>51773</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>82037</t>
+          <t>82068</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>167449</t>
+          <t>169089</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>218359</t>
+          <t>219997</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,1%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51319</t>
+          <t>51400</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>84255</t>
+          <t>84493</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57769</t>
+          <t>58511</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>88041</t>
+          <t>88181</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>118091</t>
+          <t>118565</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>163612</t>
+          <t>164398</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43881</t>
+          <t>44946</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>76131</t>
+          <t>74914</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,47 +7232,47 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>11,94%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>41607</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>31561</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>54946</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>15,99%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
           <t>12,13%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>41607</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>30270</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>54279</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>15,99%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>11,64%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>80425</t>
+          <t>80829</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>119853</t>
+          <t>118713</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>117915</t>
+          <t>117971</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>163061</t>
+          <t>160511</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>48727</t>
+          <t>49625</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>78597</t>
+          <t>78430</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>174084</t>
+          <t>177294</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>225739</t>
+          <t>228216</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,71%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>62953</t>
+          <t>62946</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>97208</t>
+          <t>95760</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12332</t>
+          <t>12076</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28906</t>
+          <t>29689</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>80695</t>
+          <t>79752</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>116779</t>
+          <t>116108</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>257760</t>
+          <t>258125</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>309227</t>
+          <t>307679</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>49878</t>
+          <t>51599</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>78703</t>
+          <t>81145</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>322067</t>
+          <t>318734</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>380025</t>
+          <t>378033</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,59%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>91861</t>
+          <t>90148</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>136487</t>
+          <t>132982</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>154051</t>
+          <t>154934</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>204409</t>
+          <t>203340</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>256464</t>
+          <t>255795</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>321668</t>
+          <t>322623</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>94057</t>
+          <t>94385</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>136849</t>
+          <t>137360</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>111570</t>
+          <t>110660</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>153140</t>
+          <t>151556</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>214159</t>
+          <t>218446</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>279786</t>
+          <t>277668</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>191404</t>
+          <t>191359</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>245658</t>
+          <t>245493</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>169682</t>
+          <t>169226</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>218990</t>
+          <t>219964</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>380036</t>
+          <t>376764</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>453200</t>
+          <t>450417</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,43%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>128752</t>
+          <t>129950</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>177459</t>
+          <t>177478</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>56352</t>
+          <t>58227</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>92212</t>
+          <t>93160</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>198240</t>
+          <t>196776</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>258931</t>
+          <t>254569</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>524636</t>
+          <t>523446</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>591236</t>
+          <t>593727</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>167697</t>
+          <t>167413</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>217727</t>
+          <t>217119</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>708269</t>
+          <t>706696</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>793934</t>
+          <t>798909</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,55%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>28390</t>
+          <t>29029</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>52273</t>
+          <t>53225</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>134313</t>
+          <t>132603</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>179463</t>
+          <t>176794</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>168681</t>
+          <t>170842</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>221448</t>
+          <t>224015</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,67%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>25388</t>
+          <t>24432</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>48685</t>
+          <t>48816</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>94299</t>
+          <t>97708</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>134630</t>
+          <t>136108</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>129065</t>
+          <t>126416</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>175390</t>
+          <t>174803</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,79%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>69934</t>
+          <t>69500</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>102548</t>
+          <t>102744</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>145168</t>
+          <t>142692</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>191387</t>
+          <t>191874</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>222029</t>
+          <t>219992</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>280795</t>
+          <t>279152</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>54845</t>
+          <t>56503</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>86807</t>
+          <t>86287</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>49117</t>
+          <t>49365</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>80324</t>
+          <t>82001</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>110860</t>
+          <t>110243</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>154811</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,21%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>259375</t>
+          <t>261937</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>304983</t>
+          <t>307026</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>233209</t>
+          <t>232314</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>284616</t>
+          <t>283557</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>503788</t>
+          <t>503923</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>574977</t>
+          <t>575007</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>45,36%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>21514</t>
+          <t>20803</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>44592</t>
+          <t>43730</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>176891</t>
+          <t>176785</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>228621</t>
+          <t>229750</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>203440</t>
+          <t>204026</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>261680</t>
+          <t>262752</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,12%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>36075</t>
+          <t>36359</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>59913</t>
+          <t>61773</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>143414</t>
+          <t>143459</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>191413</t>
+          <t>192666</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>189588</t>
+          <t>187613</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>243509</t>
+          <t>243016</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,69%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>49782</t>
+          <t>50413</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>77051</t>
+          <t>76553</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>242986</t>
+          <t>242494</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>300291</t>
+          <t>299663</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>299066</t>
+          <t>303511</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>363793</t>
+          <t>364813</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,55%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>33638</t>
+          <t>33957</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>59259</t>
+          <t>58898</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>97918</t>
+          <t>95840</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>138388</t>
+          <t>135211</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>139195</t>
+          <t>136236</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>187635</t>
+          <t>186580</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>65439</t>
+          <t>66001</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>96210</t>
+          <t>95797</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>322324</t>
+          <t>322991</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>382602</t>
+          <t>386267</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>396252</t>
+          <t>398255</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>465926</t>
+          <t>468200</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>34,08%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>328293</t>
+          <t>328012</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>402945</t>
+          <t>400639</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>745464</t>
+          <t>738813</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>848928</t>
+          <t>846096</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1101846</t>
+          <t>1098547</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1226093</t>
+          <t>1223645</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>341644</t>
+          <t>342838</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>421521</t>
+          <t>422095</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>573950</t>
+          <t>568258</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>664201</t>
+          <t>664276</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,7 +9995,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>933054</t>
+          <t>935923</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1056439</t>
+          <t>1057483</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,2%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>721174</t>
+          <t>719120</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>822064</t>
+          <t>821018</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>793187</t>
+          <t>788506</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>897472</t>
+          <t>894945</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1545942</t>
+          <t>1540739</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1694128</t>
+          <t>1683196</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,19%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>401563</t>
+          <t>403075</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>482092</t>
+          <t>480294</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>275930</t>
+          <t>275731</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>345480</t>
+          <t>346396</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>696517</t>
+          <t>698372</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>797791</t>
+          <t>806026</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1403455</t>
+          <t>1403657</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1529802</t>
+          <t>1520784</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>924849</t>
+          <t>923147</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1031431</t>
+          <t>1035495</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2360610</t>
+          <t>2362420</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2521644</t>
+          <t>2530757</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,37%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 15 o mayor el pasado verano al aire libre en 2016</t>
+          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 15 o mayor el pasado verano al aire libre en 2016 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51512</t>
+          <t>51608</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>83509</t>
+          <t>83790</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51387</t>
+          <t>50450</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>80178</t>
+          <t>80049</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>109741</t>
+          <t>110917</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>153720</t>
+          <t>153358</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>109904</t>
+          <t>110344</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>149205</t>
+          <t>149669</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>101848</t>
+          <t>104737</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>138169</t>
+          <t>139823</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>221118</t>
+          <t>222758</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>274328</t>
+          <t>274443</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,4%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81477</t>
+          <t>81897</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>118488</t>
+          <t>118437</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61543</t>
+          <t>62601</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>94753</t>
+          <t>96010</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>152113</t>
+          <t>154151</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>202428</t>
+          <t>203123</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16171</t>
+          <t>16090</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36822</t>
+          <t>37944</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12201</t>
+          <t>12233</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30176</t>
+          <t>30257</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33358</t>
+          <t>33182</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61385</t>
+          <t>62755</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>87835</t>
+          <t>90243</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>126517</t>
+          <t>127156</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52729</t>
+          <t>52599</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>83576</t>
+          <t>85364</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>150378</t>
+          <t>148358</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>197618</t>
+          <t>197889</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,52%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37742</t>
+          <t>36482</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66742</t>
+          <t>65675</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>70204</t>
+          <t>71164</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104757</t>
+          <t>104320</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>113955</t>
+          <t>113575</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>157451</t>
+          <t>159765</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,44%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63877</t>
+          <t>64524</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>97725</t>
+          <t>96401</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>103833</t>
+          <t>105179</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>141423</t>
+          <t>139765</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>176966</t>
+          <t>178354</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>225437</t>
+          <t>227654</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,54%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>79192</t>
+          <t>78393</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>112196</t>
+          <t>112584</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59067</t>
+          <t>59011</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>90901</t>
+          <t>89486</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>148164</t>
+          <t>145594</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>192431</t>
+          <t>192839</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,87%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21333</t>
+          <t>21893</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44462</t>
+          <t>42814</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12275</t>
+          <t>11914</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31166</t>
+          <t>30135</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39487</t>
+          <t>39773</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67328</t>
+          <t>66434</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101738</t>
+          <t>98870</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>139446</t>
+          <t>137352</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>55015</t>
+          <t>54089</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>86563</t>
+          <t>83566</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>164710</t>
+          <t>164398</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>214496</t>
+          <t>212805</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,55%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33202</t>
+          <t>32562</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59099</t>
+          <t>59021</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26083</t>
+          <t>25858</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47605</t>
+          <t>47717</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62230</t>
+          <t>63736</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>99424</t>
+          <t>98926</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>96661</t>
+          <t>95783</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>134928</t>
+          <t>134264</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40322</t>
+          <t>39904</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>64773</t>
+          <t>64622</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>145948</t>
+          <t>144122</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>191663</t>
+          <t>190030</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,7%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>97311</t>
+          <t>99407</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>140049</t>
+          <t>137312</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20195</t>
+          <t>20347</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>42568</t>
+          <t>40739</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>125538</t>
+          <t>125997</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>169242</t>
+          <t>168143</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,51%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34741</t>
+          <t>35002</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>61291</t>
+          <t>60530</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3666</t>
+          <t>3844</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15421</t>
+          <t>15508</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>40911</t>
+          <t>41210</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>71247</t>
+          <t>70972</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>176711</t>
+          <t>176303</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>221883</t>
+          <t>220425</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29891</t>
+          <t>29676</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52761</t>
+          <t>52439</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>214000</t>
+          <t>213123</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>265645</t>
+          <t>263353</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,38%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>83447</t>
+          <t>83292</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>121783</t>
+          <t>122498</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>137383</t>
+          <t>137997</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>183864</t>
+          <t>184014</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>233903</t>
+          <t>232741</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>293446</t>
+          <t>295415</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>198094</t>
+          <t>194919</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>249243</t>
+          <t>248351</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>232320</t>
+          <t>232830</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>284799</t>
+          <t>286395</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>441723</t>
+          <t>442491</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>523231</t>
+          <t>516066</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,23%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>230157</t>
+          <t>231261</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>288627</t>
+          <t>289359</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>151405</t>
+          <t>151583</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>198359</t>
+          <t>199268</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>397503</t>
+          <t>399864</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>473735</t>
+          <t>472707</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,02%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>88225</t>
+          <t>88570</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>128470</t>
+          <t>129127</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>34491</t>
+          <t>34520</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>59475</t>
+          <t>60071</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>131084</t>
+          <t>131793</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>178285</t>
+          <t>180430</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>420289</t>
+          <t>421414</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>483857</t>
+          <t>491249</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>161879</t>
+          <t>162082</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>212254</t>
+          <t>211309</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>593092</t>
+          <t>596059</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>680015</t>
+          <t>678613</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,49%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>37502</t>
+          <t>38107</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>65240</t>
+          <t>65171</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>105243</t>
+          <t>106837</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>145739</t>
+          <t>147625</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>151855</t>
+          <t>150107</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>202086</t>
+          <t>199739</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,7%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>76912</t>
+          <t>76588</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>115820</t>
+          <t>113468</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>166783</t>
+          <t>167459</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>216928</t>
+          <t>212806</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>253924</t>
+          <t>252577</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>314188</t>
+          <t>315330</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,2%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>92477</t>
+          <t>90881</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>129991</t>
+          <t>128450</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>126762</t>
+          <t>125994</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>171572</t>
+          <t>169917</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>228510</t>
+          <t>230160</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>286664</t>
+          <t>286166</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,06%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>44220</t>
+          <t>45421</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>72975</t>
+          <t>76062</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>36164</t>
+          <t>36060</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>63379</t>
+          <t>63696</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>87969</t>
+          <t>87554</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>127331</t>
+          <t>128701</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>285638</t>
+          <t>284676</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>335219</t>
+          <t>335394</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>201756</t>
+          <t>197581</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>250997</t>
+          <t>249390</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>503758</t>
+          <t>497716</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>571831</t>
+          <t>570670</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>41,99%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>23758</t>
+          <t>25665</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>46817</t>
+          <t>48739</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>133997</t>
+          <t>132569</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>183277</t>
+          <t>181196</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>167534</t>
+          <t>169303</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>221828</t>
+          <t>219679</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>87137</t>
+          <t>84826</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>120032</t>
+          <t>117754</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>244112</t>
+          <t>249770</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>306683</t>
+          <t>307033</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>347506</t>
+          <t>346577</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>415114</t>
+          <t>412267</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,26%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>57216</t>
+          <t>57062</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>86135</t>
+          <t>86694</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>207525</t>
+          <t>206312</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>263928</t>
+          <t>263507</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>275010</t>
+          <t>276158</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>335922</t>
+          <t>338135</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4730</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>17691</t>
+          <t>18481</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>44925</t>
+          <t>44426</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>77739</t>
+          <t>76028</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>54500</t>
+          <t>53778</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>87807</t>
+          <t>87924</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>52485</t>
+          <t>51899</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>80616</t>
+          <t>80037</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>321725</t>
+          <t>319836</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>385877</t>
+          <t>381205</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>383432</t>
+          <t>383036</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>455371</t>
+          <t>450463</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,06%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>311266</t>
+          <t>310166</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>384261</t>
+          <t>384274</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,7 +14855,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>581842</t>
+          <t>587362</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>674381</t>
+          <t>677293</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>916624</t>
+          <t>915341</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1039323</t>
+          <t>1039314</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,7 +14925,7 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>692227</t>
+          <t>691241</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>789969</t>
+          <t>786244</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>961375</t>
+          <t>962907</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1071525</t>
+          <t>1072860</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1682118</t>
+          <t>1687686</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1830595</t>
+          <t>1834116</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,6%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>708534</t>
+          <t>706108</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>803790</t>
+          <t>803663</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>687601</t>
+          <t>686118</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>782952</t>
+          <t>781994</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1416484</t>
+          <t>1416720</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1553747</t>
+          <t>1562107</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15156,7 +15156,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>245746</t>
+          <t>248801</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>311699</t>
+          <t>312037</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>175190</t>
+          <t>174303</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>232905</t>
+          <t>228499</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>438928</t>
+          <t>437068</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>518387</t>
+          <t>522662</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1198131</t>
+          <t>1195796</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1312973</t>
+          <t>1309829</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>887858</t>
+          <t>881563</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>990227</t>
+          <t>988949</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2114088</t>
+          <t>2115829</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2274037</t>
+          <t>2270355</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,92%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q4501_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q4501_R-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>69594</t>
+          <t>71358</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>105149</t>
+          <t>106078</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>79958</t>
+          <t>79870</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>112228</t>
+          <t>112775</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>157315</t>
+          <t>159556</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>205958</t>
+          <t>209915</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,94%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73549</t>
+          <t>71864</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>106775</t>
+          <t>106962</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68177</t>
+          <t>69096</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>98363</t>
+          <t>100679</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>149939</t>
+          <t>148782</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>196126</t>
+          <t>195869</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,14%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>115655</t>
+          <t>117239</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>154856</t>
+          <t>158379</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>69091</t>
+          <t>69292</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>101599</t>
+          <t>101396</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>196237</t>
+          <t>195865</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>247780</t>
+          <t>246167</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,59%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44173</t>
+          <t>43575</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73386</t>
+          <t>73103</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12820</t>
+          <t>12846</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30521</t>
+          <t>30588</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>62369</t>
+          <t>62252</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>96345</t>
+          <t>95140</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,21%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>88539</t>
+          <t>88282</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>125417</t>
+          <t>125135</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13263</t>
+          <t>13914</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31732</t>
+          <t>31408</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>108572</t>
+          <t>108027</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>152396</t>
+          <t>151326</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46244</t>
+          <t>47055</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76354</t>
+          <t>76843</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>117640</t>
+          <t>114621</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>154176</t>
+          <t>151999</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>172808</t>
+          <t>170848</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>219853</t>
+          <t>219022</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,73%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43050</t>
+          <t>43254</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>70424</t>
+          <t>69805</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63763</t>
+          <t>64685</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95544</t>
+          <t>95462</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>113653</t>
+          <t>113866</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>155274</t>
+          <t>154347</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,95%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>85551</t>
+          <t>85466</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>120752</t>
+          <t>120795</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>70867</t>
+          <t>72191</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>104406</t>
+          <t>103711</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>165991</t>
+          <t>164566</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>212724</t>
+          <t>215962</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>29,31%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37077</t>
+          <t>38133</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66589</t>
+          <t>65803</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14670</t>
+          <t>15158</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34891</t>
+          <t>34523</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58797</t>
+          <t>58188</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>92347</t>
+          <t>92969</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>79841</t>
+          <t>80534</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>115052</t>
+          <t>115790</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36222</t>
+          <t>36837</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62428</t>
+          <t>62217</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>124490</t>
+          <t>123239</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>169080</t>
+          <t>167516</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,74%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54883</t>
+          <t>55688</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86513</t>
+          <t>86622</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38870</t>
+          <t>39045</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61879</t>
+          <t>61899</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>101429</t>
+          <t>101427</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>140525</t>
+          <t>141060</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>58050</t>
+          <t>57962</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>92268</t>
+          <t>92210</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31362</t>
+          <t>31798</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>54104</t>
+          <t>52788</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>93947</t>
+          <t>95180</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>135773</t>
+          <t>137950</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>96786</t>
+          <t>95545</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>134818</t>
+          <t>134723</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>29516</t>
+          <t>29632</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>51409</t>
+          <t>51724</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>131700</t>
+          <t>129829</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>176361</t>
+          <t>174815</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>76911</t>
+          <t>76082</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>110859</t>
+          <t>112029</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5415</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19378</t>
+          <t>18484</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>84876</t>
+          <t>84785</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>125404</t>
+          <t>122323</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,22%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>172380</t>
+          <t>169778</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>216826</t>
+          <t>214804</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17284</t>
+          <t>18349</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36766</t>
+          <t>37398</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>195827</t>
+          <t>195813</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>244900</t>
+          <t>244395</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,41%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>118623</t>
+          <t>119453</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>163321</t>
+          <t>165055</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>163807</t>
+          <t>163484</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>214278</t>
+          <t>212021</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>296875</t>
+          <t>294519</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>364382</t>
+          <t>362065</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,56%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>117832</t>
+          <t>117182</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>163337</t>
+          <t>161791</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>139473</t>
+          <t>139293</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>184314</t>
+          <t>183772</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>268197</t>
+          <t>268403</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>333235</t>
+          <t>332783</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>232940</t>
+          <t>234084</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>290708</t>
+          <t>288297</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>127547</t>
+          <t>125615</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>168540</t>
+          <t>168572</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>373255</t>
+          <t>372506</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>445227</t>
+          <t>441230</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,62%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>163868</t>
+          <t>161247</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>219283</t>
+          <t>212519</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>55917</t>
+          <t>56385</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>89776</t>
+          <t>90381</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>231204</t>
+          <t>231359</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>290722</t>
+          <t>292375</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>473641</t>
+          <t>468517</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>541891</t>
+          <t>540031</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>122881</t>
+          <t>124087</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>163445</t>
+          <t>166706</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>609959</t>
+          <t>609680</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>693377</t>
+          <t>692424</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,5%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>34691</t>
+          <t>35287</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>60587</t>
+          <t>61042</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>137639</t>
+          <t>137737</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>182502</t>
+          <t>179576</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>182096</t>
+          <t>180794</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>234057</t>
+          <t>231153</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,14%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>22812</t>
+          <t>23584</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>44730</t>
+          <t>45671</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>90376</t>
+          <t>90454</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>129028</t>
+          <t>129341</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>120389</t>
+          <t>118687</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>166150</t>
+          <t>164711</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,92%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>52402</t>
+          <t>52032</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>81678</t>
+          <t>81717</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>90692</t>
+          <t>92397</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>128884</t>
+          <t>130856</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>151870</t>
+          <t>150222</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>198509</t>
+          <t>198895</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,64%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>30481</t>
+          <t>30885</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>56209</t>
+          <t>56003</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>36775</t>
+          <t>37263</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>66922</t>
+          <t>66594</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>73623</t>
+          <t>75516</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>111833</t>
+          <t>114106</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,41%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>142268</t>
+          <t>143393</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>181751</t>
+          <t>179910</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>121636</t>
+          <t>121530</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>162327</t>
+          <t>162341</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>276585</t>
+          <t>278249</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>333528</t>
+          <t>335290</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,47%</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>26401</t>
+          <t>25318</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>48265</t>
+          <t>47385</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>275886</t>
+          <t>277953</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>336393</t>
+          <t>336965</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>310974</t>
+          <t>312724</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>377945</t>
+          <t>375644</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,31%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>26495</t>
+          <t>25198</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>48031</t>
+          <t>47423</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>188013</t>
+          <t>187200</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>239598</t>
+          <t>239243</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>218173</t>
+          <t>220163</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>277988</t>
+          <t>280036</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,13%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>72139</t>
+          <t>72636</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>101875</t>
+          <t>102742</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>230426</t>
+          <t>230198</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>287306</t>
+          <t>287806</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>314039</t>
+          <t>316602</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>377751</t>
+          <t>379071</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,54%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>35479</t>
+          <t>36143</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>60799</t>
+          <t>61339</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>77624</t>
+          <t>76479</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>114163</t>
+          <t>112865</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>117802</t>
+          <t>120411</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>164206</t>
+          <t>162818</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>79168</t>
+          <t>76886</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>108662</t>
+          <t>108331</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>345109</t>
+          <t>345569</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>406091</t>
+          <t>410267</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>435269</t>
+          <t>434971</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>505714</t>
+          <t>509396</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,97%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>405327</t>
+          <t>403593</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>480522</t>
+          <t>486433</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>884718</t>
+          <t>884767</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>990172</t>
+          <t>984988</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1307653</t>
+          <t>1311462</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1444002</t>
+          <t>1441824</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>389471</t>
+          <t>389401</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>463913</t>
+          <t>464307</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>642915</t>
+          <t>639754</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>734185</t>
+          <t>736291</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1052151</t>
+          <t>1052112</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1173393</t>
+          <t>1170640</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>714978</t>
+          <t>713621</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>813754</t>
+          <t>810519</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>681131</t>
+          <t>676533</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>775428</t>
+          <t>775353</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1431122</t>
+          <t>1416999</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1562124</t>
+          <t>1551916</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,37%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>435209</t>
+          <t>439417</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>518656</t>
+          <t>522685</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>238517</t>
+          <t>234863</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>303326</t>
+          <t>302408</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>702120</t>
+          <t>692697</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>802901</t>
+          <t>797256</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1103348</t>
+          <t>1109146</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1220120</t>
+          <t>1214886</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>707647</t>
+          <t>709756</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>803962</t>
+          <t>805911</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1840520</t>
+          <t>1845982</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1987923</t>
+          <t>1990687</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,98%</t>
         </is>
       </c>
     </row>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44580</t>
+          <t>44744</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74292</t>
+          <t>75060</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>82666</t>
+          <t>82034</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>118098</t>
+          <t>116623</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>133413</t>
+          <t>132748</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>180716</t>
+          <t>180725</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47600</t>
+          <t>48437</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77459</t>
+          <t>76875</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65867</t>
+          <t>66930</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>99083</t>
+          <t>101310</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>120665</t>
+          <t>123203</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>167670</t>
+          <t>168233</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>111968</t>
+          <t>112560</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>153711</t>
+          <t>152394</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>52283</t>
+          <t>52897</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>82477</t>
+          <t>82230</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>172129</t>
+          <t>173027</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>223433</t>
+          <t>223659</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,83%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44392</t>
+          <t>43462</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73334</t>
+          <t>72708</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11535</t>
+          <t>11927</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29086</t>
+          <t>28169</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>60744</t>
+          <t>59708</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>96572</t>
+          <t>96001</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>109349</t>
+          <t>111289</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>148622</t>
+          <t>150190</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33822</t>
+          <t>33838</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59952</t>
+          <t>59467</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>151853</t>
+          <t>151956</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>200627</t>
+          <t>200401</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,73%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45578</t>
+          <t>43749</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75836</t>
+          <t>76455</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72924</t>
+          <t>72810</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>109455</t>
+          <t>106746</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>127509</t>
+          <t>127914</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>174373</t>
+          <t>175081</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48484</t>
+          <t>48393</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80485</t>
+          <t>79307</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63471</t>
+          <t>63745</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95867</t>
+          <t>94471</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>120207</t>
+          <t>118567</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>164184</t>
+          <t>166311</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>112090</t>
+          <t>112481</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>154996</t>
+          <t>151193</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>67361</t>
+          <t>67943</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>101100</t>
+          <t>101491</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>188388</t>
+          <t>189527</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>240066</t>
+          <t>241267</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,92%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25395</t>
+          <t>25124</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51112</t>
+          <t>50553</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13358</t>
+          <t>12766</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33833</t>
+          <t>32383</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42062</t>
+          <t>41416</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>72616</t>
+          <t>73744</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>110131</t>
+          <t>108344</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>152136</t>
+          <t>148458</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51773</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>82068</t>
+          <t>82498</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>169089</t>
+          <t>171995</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>219997</t>
+          <t>221514</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,3%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51400</t>
+          <t>53421</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>84493</t>
+          <t>84050</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>58511</t>
+          <t>58480</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>88181</t>
+          <t>89902</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>118565</t>
+          <t>117403</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>164398</t>
+          <t>160884</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,13%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44946</t>
+          <t>44915</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74914</t>
+          <t>76331</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31561</t>
+          <t>30311</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>54946</t>
+          <t>53879</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>80829</t>
+          <t>82404</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>118713</t>
+          <t>119613</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>117971</t>
+          <t>119761</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>160511</t>
+          <t>163308</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49625</t>
+          <t>48586</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>78430</t>
+          <t>77601</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>177294</t>
+          <t>174554</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>228216</t>
+          <t>228668</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,76%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>62946</t>
+          <t>63600</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>95760</t>
+          <t>96876</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12076</t>
+          <t>12144</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29689</t>
+          <t>29521</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>79752</t>
+          <t>80212</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>116108</t>
+          <t>118743</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258125</t>
+          <t>257785</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>307679</t>
+          <t>310357</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51599</t>
+          <t>51297</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>81145</t>
+          <t>80470</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>318734</t>
+          <t>320153</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>378033</t>
+          <t>380649</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,89%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>90148</t>
+          <t>93101</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>132982</t>
+          <t>135550</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>154934</t>
+          <t>156134</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>203340</t>
+          <t>204291</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>255795</t>
+          <t>255891</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>322623</t>
+          <t>322803</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,79%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>94385</t>
+          <t>96269</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>137360</t>
+          <t>139151</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>110660</t>
+          <t>111537</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>151556</t>
+          <t>152743</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>218446</t>
+          <t>219238</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>277668</t>
+          <t>277184</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>191359</t>
+          <t>192129</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>245493</t>
+          <t>243880</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>169226</t>
+          <t>172058</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>219964</t>
+          <t>222250</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>376764</t>
+          <t>376698</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>450417</t>
+          <t>449618</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,38%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>129950</t>
+          <t>129773</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>177478</t>
+          <t>177893</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>58227</t>
+          <t>56229</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>93160</t>
+          <t>91084</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>196776</t>
+          <t>197255</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>254569</t>
+          <t>255713</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>523446</t>
+          <t>523800</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>593727</t>
+          <t>595876</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>167413</t>
+          <t>167118</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>217119</t>
+          <t>216685</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>706696</t>
+          <t>708911</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>798909</t>
+          <t>796116</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>41,41%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29029</t>
+          <t>28698</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>53225</t>
+          <t>52590</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>132603</t>
+          <t>133945</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>176794</t>
+          <t>179950</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>170842</t>
+          <t>171294</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>224015</t>
+          <t>224250</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,69%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24432</t>
+          <t>25320</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>48816</t>
+          <t>46938</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>97708</t>
+          <t>96526</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>136108</t>
+          <t>137334</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>126416</t>
+          <t>128709</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>174803</t>
+          <t>175356</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,83%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>69500</t>
+          <t>68595</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>102744</t>
+          <t>101278</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>142692</t>
+          <t>143008</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>191874</t>
+          <t>189049</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>219992</t>
+          <t>222804</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>279152</t>
+          <t>279736</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,07%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>56503</t>
+          <t>55656</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>86287</t>
+          <t>88234</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>49365</t>
+          <t>48897</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>82001</t>
+          <t>81314</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>110243</t>
+          <t>111503</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>154811</t>
+          <t>156429</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>261937</t>
+          <t>257355</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>307026</t>
+          <t>302708</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>232314</t>
+          <t>231885</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>283557</t>
+          <t>287715</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>503923</t>
+          <t>506376</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>575007</t>
+          <t>572940</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,19%</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>20803</t>
+          <t>21106</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>43730</t>
+          <t>43224</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>176785</t>
+          <t>175994</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>229750</t>
+          <t>228026</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>204026</t>
+          <t>204453</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>262752</t>
+          <t>262395</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>36359</t>
+          <t>35766</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>61773</t>
+          <t>61384</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>143459</t>
+          <t>143589</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>192666</t>
+          <t>192937</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>187613</t>
+          <t>189199</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>243016</t>
+          <t>240695</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,52%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>50413</t>
+          <t>48962</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>76553</t>
+          <t>76242</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>242494</t>
+          <t>245761</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>299663</t>
+          <t>300512</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>303511</t>
+          <t>303617</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>364813</t>
+          <t>366489</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,67%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>33957</t>
+          <t>33117</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>58898</t>
+          <t>58962</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>95840</t>
+          <t>94880</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>135211</t>
+          <t>136903</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>136236</t>
+          <t>138069</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>186580</t>
+          <t>185923</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>66001</t>
+          <t>65136</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>95797</t>
+          <t>94814</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>322991</t>
+          <t>325180</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>386267</t>
+          <t>387820</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>398255</t>
+          <t>397436</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>468200</t>
+          <t>465583</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,88%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>328012</t>
+          <t>330396</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>400639</t>
+          <t>402252</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>738813</t>
+          <t>743864</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>846096</t>
+          <t>847967</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1098547</t>
+          <t>1096767</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1223645</t>
+          <t>1225360</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>342838</t>
+          <t>345534</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>422095</t>
+          <t>418150</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>568258</t>
+          <t>571848</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>664276</t>
+          <t>667729</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>935923</t>
+          <t>937168</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1057483</t>
+          <t>1056734</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>719120</t>
+          <t>721569</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>821018</t>
+          <t>816394</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>788506</t>
+          <t>783317</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>894945</t>
+          <t>891179</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1540739</t>
+          <t>1537835</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1683196</t>
+          <t>1681285</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,16%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>403075</t>
+          <t>400387</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>480294</t>
+          <t>484011</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>275731</t>
+          <t>277614</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>346396</t>
+          <t>345316</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>698372</t>
+          <t>698921</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>806026</t>
+          <t>800612</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,51%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1403657</t>
+          <t>1404447</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1520784</t>
+          <t>1522211</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>923147</t>
+          <t>927726</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1035495</t>
+          <t>1040032</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2362420</t>
+          <t>2358009</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2530757</t>
+          <t>2522482</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,25%</t>
         </is>
       </c>
     </row>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51608</t>
+          <t>52919</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>83790</t>
+          <t>84838</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50450</t>
+          <t>49712</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>80049</t>
+          <t>79624</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>110917</t>
+          <t>111115</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>153358</t>
+          <t>154649</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,95%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>110344</t>
+          <t>110271</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>149669</t>
+          <t>148827</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>104737</t>
+          <t>104163</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>139823</t>
+          <t>138933</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>222758</t>
+          <t>224456</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>274443</t>
+          <t>274219</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,37%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81897</t>
+          <t>84713</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>118437</t>
+          <t>121433</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62601</t>
+          <t>61087</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>96010</t>
+          <t>92660</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>154151</t>
+          <t>153417</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>203123</t>
+          <t>200712</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>25,89%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16090</t>
+          <t>16731</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37944</t>
+          <t>39597</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12233</t>
+          <t>12581</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30257</t>
+          <t>29295</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33182</t>
+          <t>33692</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62755</t>
+          <t>62698</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>90243</t>
+          <t>86921</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>127156</t>
+          <t>124210</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52599</t>
+          <t>51752</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>85364</t>
+          <t>82447</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>148358</t>
+          <t>149632</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>197889</t>
+          <t>197872</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36482</t>
+          <t>36815</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65675</t>
+          <t>64227</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>71164</t>
+          <t>70381</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104320</t>
+          <t>105971</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>113575</t>
+          <t>115035</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159765</t>
+          <t>158799</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64524</t>
+          <t>63652</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>96401</t>
+          <t>96123</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>105179</t>
+          <t>103132</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>139765</t>
+          <t>138490</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>178354</t>
+          <t>177361</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>227654</t>
+          <t>224614</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,14%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>78393</t>
+          <t>80427</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>112584</t>
+          <t>112817</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59011</t>
+          <t>57651</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>89486</t>
+          <t>89028</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>145594</t>
+          <t>147836</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>192839</t>
+          <t>192273</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,8%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21893</t>
+          <t>21514</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42814</t>
+          <t>43431</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11914</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30135</t>
+          <t>30364</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39773</t>
+          <t>39293</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66434</t>
+          <t>67460</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>98870</t>
+          <t>101038</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>137352</t>
+          <t>136698</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54089</t>
+          <t>55337</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>83566</t>
+          <t>85906</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>164398</t>
+          <t>164819</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>212805</t>
+          <t>212569</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,52%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32562</t>
+          <t>31912</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59021</t>
+          <t>58542</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25858</t>
+          <t>25151</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47717</t>
+          <t>47429</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>63736</t>
+          <t>63713</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>98926</t>
+          <t>99496</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>95783</t>
+          <t>95845</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>134264</t>
+          <t>133837</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39904</t>
+          <t>40399</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>64622</t>
+          <t>65201</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>144122</t>
+          <t>144079</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>190030</t>
+          <t>191128</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>99407</t>
+          <t>99614</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>137312</t>
+          <t>138103</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20347</t>
+          <t>20412</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40739</t>
+          <t>40578</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>125997</t>
+          <t>125068</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>168143</t>
+          <t>170293</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>35002</t>
+          <t>34561</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>60530</t>
+          <t>62086</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3844</t>
+          <t>3692</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15508</t>
+          <t>15037</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41210</t>
+          <t>41078</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>70972</t>
+          <t>71168</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>176303</t>
+          <t>175725</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>220425</t>
+          <t>219569</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29676</t>
+          <t>30074</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52439</t>
+          <t>53710</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>213123</t>
+          <t>213802</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>263353</t>
+          <t>265078</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,63%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>83292</t>
+          <t>83928</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>122498</t>
+          <t>123839</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>137997</t>
+          <t>138652</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>184014</t>
+          <t>183469</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>232741</t>
+          <t>231480</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>295415</t>
+          <t>296010</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>194919</t>
+          <t>195103</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>248351</t>
+          <t>250149</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>232830</t>
+          <t>231850</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>286395</t>
+          <t>285273</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>442491</t>
+          <t>438920</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>516066</t>
+          <t>519329</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,39%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>231261</t>
+          <t>231582</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>289359</t>
+          <t>290752</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>151583</t>
+          <t>154113</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>199268</t>
+          <t>200442</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>399864</t>
+          <t>398203</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>472707</t>
+          <t>472437</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,01%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>88570</t>
+          <t>87378</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>129127</t>
+          <t>127392</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>34520</t>
+          <t>35047</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>60071</t>
+          <t>61758</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>131793</t>
+          <t>129220</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>180430</t>
+          <t>177659</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>421414</t>
+          <t>421426</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>491249</t>
+          <t>485385</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>162082</t>
+          <t>158530</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>211309</t>
+          <t>208967</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>596059</t>
+          <t>596918</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>678613</t>
+          <t>678436</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,48%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>38107</t>
+          <t>37495</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>65171</t>
+          <t>65329</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>106837</t>
+          <t>105329</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>147625</t>
+          <t>147608</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>150107</t>
+          <t>149691</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>199739</t>
+          <t>201798</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>76588</t>
+          <t>76903</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>113468</t>
+          <t>113272</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>167459</t>
+          <t>164634</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>212806</t>
+          <t>214998</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>252577</t>
+          <t>255037</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>315330</t>
+          <t>317620</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,37%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>90881</t>
+          <t>89323</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>128450</t>
+          <t>126978</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>125994</t>
+          <t>126491</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>169917</t>
+          <t>171707</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>230160</t>
+          <t>230625</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>286166</t>
+          <t>288709</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>45421</t>
+          <t>44487</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>76062</t>
+          <t>73255</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>36060</t>
+          <t>35638</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>63696</t>
+          <t>62890</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>87554</t>
+          <t>87267</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>128701</t>
+          <t>127411</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>284676</t>
+          <t>286503</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>335394</t>
+          <t>336926</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>197581</t>
+          <t>199504</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>249390</t>
+          <t>250753</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>497716</t>
+          <t>498867</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>570670</t>
+          <t>570083</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>41,95%</t>
         </is>
       </c>
     </row>
@@ -14138,7 +14138,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>25665</t>
+          <t>25770</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>48739</t>
+          <t>48910</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>132569</t>
+          <t>134109</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>181196</t>
+          <t>180988</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>169303</t>
+          <t>168386</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>219679</t>
+          <t>220280</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,17%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>84826</t>
+          <t>85206</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>117754</t>
+          <t>118765</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>249770</t>
+          <t>248119</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>307033</t>
+          <t>306084</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>346577</t>
+          <t>345254</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>412267</t>
+          <t>415860</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,52%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>57062</t>
+          <t>56867</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>86694</t>
+          <t>86327</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>206312</t>
+          <t>207564</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>263507</t>
+          <t>262349</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>276158</t>
+          <t>275424</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>338135</t>
+          <t>340113</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,96%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>4816</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>18481</t>
+          <t>18600</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>44426</t>
+          <t>45642</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>76028</t>
+          <t>77576</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>53778</t>
+          <t>54004</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>87924</t>
+          <t>89608</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>51899</t>
+          <t>50831</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>80037</t>
+          <t>80425</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>319836</t>
+          <t>319349</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>381205</t>
+          <t>383942</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>383036</t>
+          <t>381172</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>450463</t>
+          <t>452308</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,2%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>310166</t>
+          <t>312941</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>384274</t>
+          <t>389053</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>587362</t>
+          <t>584684</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>677293</t>
+          <t>678405</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>915341</t>
+          <t>917326</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1039314</t>
+          <t>1040713</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,09%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>691241</t>
+          <t>696506</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>786244</t>
+          <t>790653</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>962907</t>
+          <t>958330</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1072860</t>
+          <t>1074045</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1687686</t>
+          <t>1691305</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1834116</t>
+          <t>1836211</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,63%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>706108</t>
+          <t>703785</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>803663</t>
+          <t>797134</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>686118</t>
+          <t>680614</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>781994</t>
+          <t>784687</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1416720</t>
+          <t>1422295</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1562107</t>
+          <t>1563672</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>248801</t>
+          <t>247901</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>312037</t>
+          <t>312270</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>174303</t>
+          <t>173489</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>228499</t>
+          <t>229039</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>437068</t>
+          <t>440355</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>522662</t>
+          <t>524135</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1195796</t>
+          <t>1197630</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1309829</t>
+          <t>1313002</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>881563</t>
+          <t>886044</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>988949</t>
+          <t>993061</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2115829</t>
+          <t>2115199</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2270355</t>
+          <t>2264324</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,84%</t>
         </is>
       </c>
     </row>
